--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484243_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484243_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. BELVER EDO</t>
+          <t>M. PAGES SAUQUE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3156</v>
+        <v>2.7256</v>
       </c>
       <c r="E2" t="n">
-        <v>5.8926</v>
+        <v>5.3222</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.577</v>
+        <v>-2.5966</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2462</v>
+        <v>1.6843</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0445</v>
+        <v>0.349</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.2908</v>
+        <v>1.3354</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5639</v>
+        <v>4.0623</v>
       </c>
       <c r="K2" t="n">
-        <v>4.8312</v>
+        <v>0.1637</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.2673</v>
+        <v>3.8985</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.8101</v>
+        <v>-2.3779</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.7866</v>
+        <v>0.1852</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.0235</v>
+        <v>-2.5632</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.1488</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1.1721</v>
       </c>
       <c r="S2" t="n">
-        <v>1.7691</v>
+        <v>-0.1308</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4308</v>
+        <v>0.0413</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3383</v>
+        <v>-0.1721</v>
       </c>
       <c r="V2" t="n">
-        <v>2.7693</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>3.0466</v>
+        <v>1.2186</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.2772</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. PAGES SAUQUE</t>
+          <t>I. BELVER EDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4029</v>
+        <v>2.3705</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9177</v>
+        <v>5.0836</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.5149</v>
+        <v>-2.7132</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6843</v>
+        <v>-0.2462</v>
       </c>
       <c r="H3" t="n">
-        <v>0.349</v>
+        <v>3.0445</v>
       </c>
       <c r="I3" t="n">
-        <v>1.3354</v>
+        <v>-3.2908</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0623</v>
+        <v>3.5639</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1637</v>
+        <v>4.8312</v>
       </c>
       <c r="L3" t="n">
-        <v>3.8985</v>
+        <v>-1.2673</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3779</v>
+        <v>-3.8101</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1852</v>
+        <v>-1.7866</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.5632</v>
+        <v>-2.0235</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.1488</v>
       </c>
       <c r="R3" t="n">
         <v>1.1721</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4535</v>
+        <v>0.8241000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3631</v>
+        <v>0.6219</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.09039999999999999</v>
+        <v>0.2021</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>2.7693</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2186</v>
+        <v>3.0466</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2976</v>
+        <v>0.6826</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5756</v>
+        <v>2.2834</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.8732</v>
+        <v>-1.6009</v>
       </c>
       <c r="G4" t="n">
         <v>-0.4852</v>
@@ -766,13 +766,13 @@
         <v>1.9534</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7538</v>
+        <v>0.2263</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6657</v>
+        <v>0.0421</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0881</v>
+        <v>0.1843</v>
       </c>
       <c r="V4" t="n">
         <v>0.9414</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4836</v>
+        <v>-0.0589</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4836</v>
+        <v>2.2861</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.9672</v>
+        <v>-2.3451</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.5682</v>
+        <v>-3.0762</v>
       </c>
       <c r="H5" t="n">
-        <v>1.4012</v>
+        <v>0.7933</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.9694</v>
+        <v>-3.8695</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2143</v>
+        <v>1.6084</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3507</v>
+        <v>2.3753</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8636</v>
+        <v>-0.7669</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7826</v>
+        <v>-4.6846</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0504</v>
+        <v>-1.582</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.833</v>
+        <v>-3.1026</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0148</v>
+        <v>0.3997</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3715</v>
+        <v>0.3186</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3567</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8279</v>
+        <v>0.6642</v>
       </c>
       <c r="W5" t="n">
-        <v>1.8279</v>
+        <v>0.5545</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.1097</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9417</v>
+        <v>-0.6119</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3761</v>
+        <v>1.3825</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3178</v>
+        <v>-1.9944</v>
       </c>
       <c r="G6" t="n">
-        <v>-3.0762</v>
+        <v>-0.5682</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7933</v>
+        <v>1.4012</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.8695</v>
+        <v>-1.9694</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6084</v>
+        <v>2.2143</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3753</v>
+        <v>1.3507</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7669</v>
+        <v>0.8636</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.6846</v>
+        <v>-2.7826</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.582</v>
+        <v>0.0504</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.1026</v>
+        <v>-2.833</v>
       </c>
       <c r="P6" t="n">
-        <v>1.9534</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1953</v>
+        <v>-2.9301</v>
       </c>
       <c r="R6" t="n">
-        <v>2.1488</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4831</v>
+        <v>-0.1135</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5915</v>
+        <v>0.2704</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1083</v>
+        <v>-0.3839</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6642</v>
+        <v>1.8279</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5545</v>
+        <v>1.8279</v>
       </c>
       <c r="X6" t="n">
-        <v>0.1097</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1259</v>
+        <v>-1.1181</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0529</v>
+        <v>1.9518</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.1788</v>
+        <v>-3.0699</v>
       </c>
       <c r="G7" t="n">
         <v>-0.08699999999999999</v>
@@ -1000,13 +1000,13 @@
         <v>0.3907</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2575</v>
+        <v>-0.2497</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3853</v>
+        <v>0.2841</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6428</v>
+        <v>-0.5339</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. SOTO CAPARROS</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4122</v>
+        <v>-2.3013</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0245</v>
+        <v>1.2512</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.3877</v>
+        <v>-3.5525</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.5256</v>
+        <v>1.0893</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.3654</v>
+        <v>1.1435</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1603</v>
+        <v>-0.0543</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0798</v>
+        <v>3.1275</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6486</v>
+        <v>1.0233</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7284</v>
+        <v>2.1042</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.6055</v>
+        <v>-2.0382</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7168</v>
+        <v>0.1203</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8887</v>
+        <v>-2.1585</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1488</v>
+        <v>-2.9301</v>
       </c>
       <c r="R8" t="n">
         <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>2.0939</v>
+        <v>0.2503</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0444</v>
+        <v>0.4994</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0495</v>
+        <v>-0.2491</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9962</v>
+        <v>-1.8828</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X8" t="n">
-        <v>0.9962</v>
+        <v>-2.4373</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>A. SOTO CAPARROS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6674</v>
+        <v>-2.5905</v>
       </c>
       <c r="E9" t="n">
-        <v>1.8579</v>
+        <v>-1.339</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.5253</v>
+        <v>-1.2515</v>
       </c>
       <c r="G9" t="n">
-        <v>1.0893</v>
+        <v>-3.5256</v>
       </c>
       <c r="H9" t="n">
-        <v>1.1435</v>
+        <v>-2.3654</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0543</v>
+        <v>-1.1603</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1275</v>
+        <v>0.0798</v>
       </c>
       <c r="K9" t="n">
-        <v>1.0233</v>
+        <v>-0.6486</v>
       </c>
       <c r="L9" t="n">
-        <v>2.1042</v>
+        <v>0.7284</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.0382</v>
+        <v>-3.6055</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1203</v>
+        <v>-1.7168</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1585</v>
+        <v>-1.8887</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.7581</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-2.1488</v>
       </c>
       <c r="R9" t="n">
         <v>1.1721</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8843</v>
+        <v>0.9156</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1061</v>
+        <v>0.7299</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2218</v>
+        <v>0.1856</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8828</v>
+        <v>0.9962</v>
       </c>
       <c r="W9" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.4373</v>
+        <v>0.9962</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1114</v>
+        <v>-4.8315</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.682</v>
+        <v>-3.0753</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4294</v>
+        <v>-1.7562</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9381</v>
@@ -1234,13 +1234,13 @@
         <v>0.9767</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2993</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4237</v>
+        <v>0.183</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7229</v>
+        <v>0.3961</v>
       </c>
       <c r="V10" t="n">
         <v>-1.4959</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-9.084</v>
+        <v>-8.6717</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2586</v>
+        <v>-2.9552</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.8254</v>
+        <v>-5.7165</v>
       </c>
       <c r="G11" t="n">
         <v>-5.008</v>
@@ -1312,13 +1312,13 @@
         <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8573</v>
+        <v>-0.4451</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3494</v>
+        <v>-0.046</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.508</v>
+        <v>-0.399</v>
       </c>
       <c r="V11" t="n">
         <v>-2.4373</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.4053</v>
+        <v>-14.4052</v>
       </c>
       <c r="E12" t="n">
         <v>12.1913</v>
       </c>
       <c r="F12" t="n">
-        <v>-26.59670000000001</v>
+        <v>-26.5968</v>
       </c>
       <c r="G12" t="n">
         <v>-13.1609</v>
       </c>
       <c r="H12" t="n">
-        <v>2.347100000000001</v>
+        <v>2.347099999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-15.5082</v>
@@ -1390,13 +1390,13 @@
         <v>11.7208</v>
       </c>
       <c r="S12" t="n">
-        <v>2.256200000000001</v>
+        <v>2.256</v>
       </c>
       <c r="T12" t="n">
         <v>2.9447</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6888000000000002</v>
+        <v>-0.6888000000000001</v>
       </c>
       <c r="V12" t="n">
         <v>1.383</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.7502</v>
+        <v>11.7931</v>
       </c>
       <c r="E13" t="n">
-        <v>14.9413</v>
+        <v>14.739</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1911</v>
+        <v>-2.946</v>
       </c>
       <c r="G13" t="n">
         <v>5.8872</v>
@@ -1468,13 +1468,13 @@
         <v>2.3441</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4143</v>
+        <v>-0.3714</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5009</v>
+        <v>0.2987</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.9151</v>
+        <v>-0.67</v>
       </c>
       <c r="V13" t="n">
         <v>3.9331</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.0258</v>
+        <v>6.4562</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1137</v>
+        <v>6.5182</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.08790000000000001</v>
+        <v>-0.062</v>
       </c>
       <c r="G14" t="n">
         <v>7.5442</v>
@@ -1546,13 +1546,13 @@
         <v>2.7348</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7138</v>
+        <v>-0.2834</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2337</v>
+        <v>0.1707</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.48</v>
+        <v>-0.4541</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6093</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.6642</v>
+        <v>2.2307</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9516</v>
+        <v>2.3561</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2875</v>
+        <v>-0.1254</v>
       </c>
       <c r="G15" t="n">
         <v>1.9294</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0466</v>
+        <v>-0.4801</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7262999999999999</v>
+        <v>-0.3218</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3204</v>
+        <v>-0.1583</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>M. CORBERA BUSQUETA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.323</v>
+        <v>1.4472</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0375</v>
+        <v>2.9944</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7145</v>
+        <v>-1.5471</v>
       </c>
       <c r="G16" t="n">
-        <v>1.3091</v>
+        <v>2.0899</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.2901</v>
+        <v>1.1328</v>
       </c>
       <c r="I16" t="n">
-        <v>4.5993</v>
+        <v>0.9572000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1207</v>
+        <v>3.1984</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.0195</v>
+        <v>2.3753</v>
       </c>
       <c r="L16" t="n">
-        <v>5.1401</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.8115</v>
+        <v>-1.1085</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.2707</v>
+        <v>-1.2425</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5409</v>
+        <v>0.134</v>
       </c>
       <c r="P16" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q16" t="n">
         <v>-0.9767</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-3.9069</v>
-      </c>
       <c r="R16" t="n">
-        <v>2.9301</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9319</v>
+        <v>-0.4278</v>
       </c>
       <c r="T16" t="n">
-        <v>1.5465</v>
+        <v>-0.0591</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3855</v>
+        <v>-0.3688</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.9414</v>
+        <v>-0.9962</v>
       </c>
       <c r="W16" t="n">
-        <v>0.2772</v>
+        <v>0.8317</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2186</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7503</v>
+        <v>1.278</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0041</v>
+        <v>0.1981</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7544</v>
+        <v>1.0799</v>
       </c>
       <c r="G17" t="n">
         <v>0.2931</v>
@@ -1780,13 +1780,13 @@
         <v>0.9767</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5195</v>
+        <v>0.008200000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2421</v>
+        <v>-0.0399</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2774</v>
+        <v>0.0481</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. CORBERA BUSQUETA</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5423</v>
+        <v>-0.2809</v>
       </c>
       <c r="E18" t="n">
-        <v>2.3877</v>
+        <v>0.9252</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.8453</v>
+        <v>-1.2061</v>
       </c>
       <c r="G18" t="n">
-        <v>2.0899</v>
+        <v>1.3091</v>
       </c>
       <c r="H18" t="n">
-        <v>1.1328</v>
+        <v>-3.2901</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9572000000000001</v>
+        <v>4.5993</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1984</v>
+        <v>4.1207</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3753</v>
+        <v>-1.0195</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8231000000000001</v>
+        <v>5.1401</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1085</v>
+        <v>-2.8115</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.2425</v>
+        <v>-2.2707</v>
       </c>
       <c r="O18" t="n">
-        <v>0.134</v>
+        <v>-0.5409</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>-3.9069</v>
       </c>
       <c r="R18" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3328</v>
+        <v>0.3281</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6657</v>
+        <v>0.4342</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.667</v>
+        <v>-0.1061</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9962</v>
+        <v>-0.9414</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8317</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="19">
@@ -1891,10 +1891,10 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0668</v>
+        <v>-0.6735</v>
       </c>
       <c r="E19" t="n">
-        <v>2.3455</v>
+        <v>1.7388</v>
       </c>
       <c r="F19" t="n">
         <v>-2.4123</v>
@@ -1936,10 +1936,10 @@
         <v>0.7814</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1061</v>
+        <v>0.4994</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1061</v>
+        <v>0.4994</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5395</v>
+        <v>-3.5852</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.2498</v>
+        <v>-0.5221</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2896</v>
+        <v>-3.0631</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.1578</v>
+        <v>-3.0339</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1594</v>
+        <v>-1.24</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9984</v>
+        <v>-1.7939</v>
       </c>
       <c r="J20" t="n">
-        <v>0.3594</v>
+        <v>-0.3213</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1433</v>
+        <v>-0.5513</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2161</v>
+        <v>0.23</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5172</v>
+        <v>-2.7125</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3026</v>
+        <v>-0.6887</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2146</v>
+        <v>-2.0239</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9534</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3268</v>
+        <v>-0.4815</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0083</v>
+        <v>-0.2008</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3352</v>
+        <v>-0.2807</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6642</v>
+        <v>-1.8279</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0441</v>
+        <v>-3.5861</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9266</v>
+        <v>-2.351</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1176</v>
+        <v>-1.2352</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0339</v>
+        <v>-2.1578</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.24</v>
+        <v>-1.1594</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7939</v>
+        <v>-0.9984</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.3213</v>
+        <v>0.3594</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.5513</v>
+        <v>0.1433</v>
       </c>
       <c r="L21" t="n">
-        <v>0.23</v>
+        <v>0.2161</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7125</v>
+        <v>-2.5172</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6887</v>
+        <v>-1.3026</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.0239</v>
+        <v>-1.2146</v>
       </c>
       <c r="P21" t="n">
-        <v>1.7581</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q21" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S21" t="n">
+        <v>-0.3735</v>
+      </c>
+      <c r="T21" t="n">
+        <v>-0.09279999999999999</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-0.2807</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.7581</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.9404</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.6052</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.3352</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-1.8279</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-1.8279</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>14.4054</v>
+        <v>15.0795</v>
       </c>
       <c r="E22" t="n">
-        <v>26.5968</v>
+        <v>26.5967</v>
       </c>
       <c r="F22" t="n">
-        <v>-12.1914</v>
+        <v>-11.5173</v>
       </c>
       <c r="G22" t="n">
         <v>13.1609</v>
@@ -2170,13 +2170,13 @@
         <v>16.6041</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.2562</v>
+        <v>-1.582</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6888000000000003</v>
+        <v>0.6886000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.9448</v>
+        <v>-2.2706</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3831</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484243_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484243_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-1.2186</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,11 +798,16 @@
       <c r="X4" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. REAL LOPEZ</t>
+          <t>G. VIÑALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0589</v>
+        <v>0.607</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2861</v>
+        <v>0.607</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.3451</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.0762</v>
+        <v>0.607</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7933</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.8695</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>1.6084</v>
+        <v>0.607</v>
       </c>
       <c r="K5" t="n">
-        <v>2.3753</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7669</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.6846</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.582</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.1026</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.1488</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3997</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3186</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.08110000000000001</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6642</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1097</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ MARIN</t>
+          <t>A. REAL LOPEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.6119</v>
+        <v>-0.0589</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3825</v>
+        <v>2.2861</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9944</v>
+        <v>-2.3451</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.5682</v>
+        <v>-3.0762</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4012</v>
+        <v>0.7933</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.9694</v>
+        <v>-3.8695</v>
       </c>
       <c r="J6" t="n">
-        <v>2.2143</v>
+        <v>1.6084</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3507</v>
+        <v>2.3753</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8636</v>
+        <v>-0.7669</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.7826</v>
+        <v>-4.6846</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0504</v>
+        <v>-1.582</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.833</v>
+        <v>-3.1026</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.7581</v>
+        <v>1.9534</v>
       </c>
       <c r="Q6" t="n">
-        <v>-2.9301</v>
+        <v>-0.1953</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>2.1488</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.1135</v>
+        <v>0.3997</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2704</v>
+        <v>0.3186</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3839</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8279</v>
+        <v>0.6642</v>
       </c>
       <c r="W6" t="n">
-        <v>1.8279</v>
+        <v>0.5545</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>0.1097</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. MARZO CHECA</t>
+          <t>J. RODRIGUEZ MARIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.1181</v>
+        <v>-0.6119</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9518</v>
+        <v>1.3825</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.0699</v>
+        <v>-1.9944</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.5682</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7355</v>
+        <v>1.4012</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.8225</v>
+        <v>-1.9694</v>
       </c>
       <c r="J7" t="n">
-        <v>2.8397</v>
+        <v>2.2143</v>
       </c>
       <c r="K7" t="n">
-        <v>1.6385</v>
+        <v>1.3507</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2011</v>
+        <v>0.8636</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.9267</v>
+        <v>-2.7826</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.903</v>
+        <v>0.0504</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.0237</v>
+        <v>-2.833</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.7814</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1721</v>
+        <v>-2.9301</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3907</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2497</v>
+        <v>-0.1135</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2841</v>
+        <v>0.2704</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5339</v>
+        <v>-0.3839</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8279</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. VIÑALLONGA BLANCO</t>
+          <t>C. MARZO CHECA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1068,72 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.3013</v>
+        <v>-1.1181</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2512</v>
+        <v>1.9518</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.5525</v>
+        <v>-3.0699</v>
       </c>
       <c r="G8" t="n">
-        <v>1.0893</v>
+        <v>-0.08699999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.1435</v>
+        <v>0.7355</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0543</v>
+        <v>-0.8225</v>
       </c>
       <c r="J8" t="n">
-        <v>3.1275</v>
+        <v>2.8397</v>
       </c>
       <c r="K8" t="n">
-        <v>1.0233</v>
+        <v>1.6385</v>
       </c>
       <c r="L8" t="n">
-        <v>2.1042</v>
+        <v>1.2011</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0382</v>
+        <v>-2.9267</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1203</v>
+        <v>-0.903</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.1585</v>
+        <v>-2.0237</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.7581</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.9301</v>
+        <v>-1.1721</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>0.3907</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2503</v>
+        <v>-0.2497</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4994</v>
+        <v>0.2841</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2491</v>
+        <v>-0.5339</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-2.4373</v>
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -1173,11 +1213,16 @@
       <c r="X9" t="n">
         <v>0.9962</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. REYES QUEZADA</t>
+          <t>G. VINALLONGA BLANCO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8315</v>
+        <v>-2.9083</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.0753</v>
+        <v>0.6443</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7562</v>
+        <v>-3.5525</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.9381</v>
+        <v>0.4823</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.6035</v>
+        <v>1.1435</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.3346</v>
+        <v>-0.6613</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.3049</v>
+        <v>2.5205</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1845</v>
+        <v>1.0233</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1204</v>
+        <v>1.4972</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6332</v>
+        <v>-2.0382</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.419</v>
+        <v>0.1203</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2142</v>
+        <v>-2.1585</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>-1.7581</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5790999999999999</v>
+        <v>0.2503</v>
       </c>
       <c r="T10" t="n">
-        <v>0.183</v>
+        <v>0.4994</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3961</v>
+        <v>-0.2491</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4959</v>
+        <v>-1.8828</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.4959</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. AURO GARRIGA</t>
+          <t>A. REYES QUEZADA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-8.6717</v>
+        <v>-4.8315</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.9552</v>
+        <v>-3.0753</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.7165</v>
+        <v>-1.7562</v>
       </c>
       <c r="G11" t="n">
-        <v>-5.008</v>
+        <v>-2.9381</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.0274</v>
+        <v>-1.6035</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.9806</v>
+        <v>-1.3346</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.7372</v>
+        <v>-1.3049</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.5104</v>
+        <v>-1.1845</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2268</v>
+        <v>-0.1204</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.2708</v>
+        <v>-1.6332</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.517</v>
+        <v>-0.419</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.7538</v>
+        <v>-1.2142</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.7814</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-1.9534</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4451</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.046</v>
+        <v>0.183</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.399</v>
+        <v>0.3961</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4373</v>
+        <v>-1.4959</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.4373</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>J. AURO GARRIGA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,151 +1400,157 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-14.4052</v>
+        <v>-8.6717</v>
       </c>
       <c r="E12" t="n">
-        <v>12.1913</v>
+        <v>-2.9552</v>
       </c>
       <c r="F12" t="n">
-        <v>-26.5968</v>
+        <v>-5.7165</v>
       </c>
       <c r="G12" t="n">
-        <v>-13.1609</v>
+        <v>-5.008</v>
       </c>
       <c r="H12" t="n">
-        <v>2.347099999999999</v>
+        <v>-2.0274</v>
       </c>
       <c r="I12" t="n">
-        <v>-15.5082</v>
+        <v>-2.9806</v>
       </c>
       <c r="J12" t="n">
-        <v>17.43</v>
+        <v>-1.7372</v>
       </c>
       <c r="K12" t="n">
-        <v>10.679</v>
+        <v>-0.5104</v>
       </c>
       <c r="L12" t="n">
-        <v>6.750800000000001</v>
+        <v>-1.2268</v>
       </c>
       <c r="M12" t="n">
-        <v>-30.5909</v>
+        <v>-3.2708</v>
       </c>
       <c r="N12" t="n">
-        <v>-8.331899999999999</v>
+        <v>-1.517</v>
       </c>
       <c r="O12" t="n">
-        <v>-22.2592</v>
+        <v>-1.7538</v>
       </c>
       <c r="P12" t="n">
-        <v>-4.883599999999999</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q12" t="n">
-        <v>-16.6041</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>11.7208</v>
+        <v>0.3907</v>
       </c>
       <c r="S12" t="n">
-        <v>2.256</v>
+        <v>-0.4451</v>
       </c>
       <c r="T12" t="n">
-        <v>2.9447</v>
+        <v>-0.046</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.6888000000000001</v>
+        <v>-0.399</v>
       </c>
       <c r="V12" t="n">
-        <v>1.383</v>
+        <v>-2.4373</v>
       </c>
       <c r="W12" t="n">
-        <v>8.4207</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-7.037599999999999</v>
+        <v>-2.4373</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. HERNANDEZ GIMENEZ</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+          <t>DM GROUP MOLLET</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.7931</v>
+        <v>-14.4052</v>
       </c>
       <c r="E13" t="n">
-        <v>14.739</v>
+        <v>12.1914</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.946</v>
+        <v>-26.5968</v>
       </c>
       <c r="G13" t="n">
-        <v>5.8872</v>
+        <v>-13.1609</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.0468</v>
+        <v>2.347099999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>5.9341</v>
+        <v>-15.5082</v>
       </c>
       <c r="J13" t="n">
-        <v>9.288600000000001</v>
+        <v>17.43</v>
       </c>
       <c r="K13" t="n">
-        <v>1.6001</v>
+        <v>10.679</v>
       </c>
       <c r="L13" t="n">
-        <v>7.6885</v>
+        <v>6.750800000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.4014</v>
+        <v>-30.5909</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.647</v>
+        <v>-8.331899999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7544</v>
+        <v>-22.2592</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3441</v>
+        <v>-4.883599999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-16.6041</v>
       </c>
       <c r="R13" t="n">
-        <v>2.3441</v>
+        <v>11.7208</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3714</v>
+        <v>2.256</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2987</v>
+        <v>2.9447</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.67</v>
+        <v>-0.6888</v>
       </c>
       <c r="V13" t="n">
-        <v>3.9331</v>
+        <v>1.383</v>
       </c>
       <c r="W13" t="n">
-        <v>5.1517</v>
+        <v>8.4207</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.2186</v>
-      </c>
+        <v>-7.037599999999999</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>J. GASCON TORNE</t>
+          <t>J. HERNANDEZ GIMENEZ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.4562</v>
+        <v>11.7931</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5182</v>
+        <v>14.739</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.062</v>
+        <v>-2.946</v>
       </c>
       <c r="G14" t="n">
-        <v>7.5442</v>
+        <v>5.8872</v>
       </c>
       <c r="H14" t="n">
-        <v>2.9051</v>
+        <v>-0.0468</v>
       </c>
       <c r="I14" t="n">
-        <v>4.6391</v>
+        <v>5.9341</v>
       </c>
       <c r="J14" t="n">
-        <v>9.3325</v>
+        <v>9.288600000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0176</v>
+        <v>1.6001</v>
       </c>
       <c r="L14" t="n">
-        <v>5.3148</v>
+        <v>7.6885</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7882</v>
+        <v>-3.4014</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1125</v>
+        <v>-1.647</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6757</v>
+        <v>-1.7544</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>2.3441</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.9301</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7348</v>
+        <v>2.3441</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2834</v>
+        <v>-0.3714</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1707</v>
+        <v>0.2987</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4541</v>
+        <v>-0.67</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6093</v>
+        <v>3.9331</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.0549</v>
+        <v>5.1517</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5545</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. GARCÍA RIERA</t>
+          <t>J. GASCON TORNE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1645,72 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.2307</v>
+        <v>6.4562</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3561</v>
+        <v>6.5182</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1254</v>
+        <v>-0.062</v>
       </c>
       <c r="G15" t="n">
-        <v>1.9294</v>
+        <v>7.5442</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5405</v>
+        <v>2.9051</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3889</v>
+        <v>4.6391</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3774</v>
+        <v>9.3325</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9877</v>
+        <v>4.0176</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3897</v>
+        <v>5.3148</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.448</v>
+        <v>-1.7882</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4472</v>
+        <v>-1.1125</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0008</v>
+        <v>-0.6757</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7814</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>-2.9301</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>2.7348</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4801</v>
+        <v>-0.2834</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3218</v>
+        <v>0.1707</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1583</v>
+        <v>-0.4541</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2772</v>
+        <v>-0.0549</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-1.8279</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,11 +1873,16 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. LLUFRIU ARCOS</t>
+          <t>G. GARCÍA RIERA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2809</v>
+        <v>1.221</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9252</v>
+        <v>1.221</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.2061</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>1.3091</v>
+        <v>1.221</v>
       </c>
       <c r="H18" t="n">
-        <v>-3.2901</v>
+        <v>0.614</v>
       </c>
       <c r="I18" t="n">
-        <v>4.5993</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1207</v>
+        <v>1.221</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.0195</v>
+        <v>0.614</v>
       </c>
       <c r="L18" t="n">
-        <v>5.1401</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.8115</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.2707</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5409</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.9301</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4342</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1061</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9414</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GOMEZ PRIVAT</t>
+          <t>G. GARCIA RIERA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6735</v>
+        <v>1.0097</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7388</v>
+        <v>1.1351</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4123</v>
+        <v>-0.1254</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.7003</v>
+        <v>0.7085</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5789</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.1214</v>
+        <v>0.7819</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9974</v>
+        <v>2.1564</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3095</v>
+        <v>1.3737</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>0.7827</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6978</v>
+        <v>-1.448</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8885</v>
+        <v>-1.4472</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8093</v>
+        <v>-0.0008</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.1953</v>
+        <v>0.7814</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4994</v>
+        <v>-0.4801</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4994</v>
+        <v>-0.3218</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>-0.1583</v>
       </c>
       <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X19" t="n">
         <v>-0.2772</v>
       </c>
-      <c r="W19" t="n">
-        <v>1.2186</v>
-      </c>
-      <c r="X19" t="n">
-        <v>-1.4959</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>P. BAGUR PONS</t>
+          <t>S. LLUFRIU ARCOS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5852</v>
+        <v>-0.2809</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5221</v>
+        <v>0.9252</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.0631</v>
+        <v>-1.2061</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.0339</v>
+        <v>1.3091</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.24</v>
+        <v>-3.2901</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7939</v>
+        <v>4.5993</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3213</v>
+        <v>4.1207</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5513</v>
+        <v>-1.0195</v>
       </c>
       <c r="L20" t="n">
-        <v>0.23</v>
+        <v>5.1401</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7125</v>
+        <v>-2.8115</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6887</v>
+        <v>-2.2707</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.0239</v>
+        <v>-0.5409</v>
       </c>
       <c r="P20" t="n">
-        <v>1.7581</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R20" t="n">
-        <v>1.7581</v>
+        <v>2.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4815</v>
+        <v>0.3281</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2008</v>
+        <v>0.4342</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2807</v>
+        <v>-0.1061</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8279</v>
+        <v>-0.9414</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.8279</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. FERNANDEZ RODRIGUEZ</t>
+          <t>R. GOMEZ PRIVAT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.5861</v>
+        <v>-0.6735</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.351</v>
+        <v>1.7388</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2352</v>
+        <v>-2.4123</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1578</v>
+        <v>-0.7003</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1594</v>
+        <v>-0.5789</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.9984</v>
+        <v>-0.1214</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3594</v>
+        <v>0.9974</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1433</v>
+        <v>0.3095</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2161</v>
+        <v>0.6879</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.5172</v>
+        <v>-1.6978</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3026</v>
+        <v>-0.8885</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2146</v>
+        <v>-0.8093</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0.7814</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3735</v>
+        <v>0.4994</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.09279999999999999</v>
+        <v>0.4994</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2807</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6642</v>
+        <v>-0.2772</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6642</v>
+        <v>1.2186</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.4959</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. BAGUR PONS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,235 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
+        <v>-3.5852</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.5221</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.0631</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-3.0339</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-1.24</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-1.7939</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-0.3213</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.5513</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-2.7125</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.6887</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-2.0239</v>
+      </c>
+      <c r="P22" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.4815</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.2008</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.2807</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-1.8279</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>V. FERNANDEZ RODRIGUEZ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-3.5861</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-2.351</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-1.2352</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-2.1578</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-1.1594</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.9984</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.3594</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.1433</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.2161</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-2.5172</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.3026</v>
+      </c>
+      <c r="O23" t="n">
+        <v>-1.2146</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.3907</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S23" t="n">
+        <v>-0.3735</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.09279999999999999</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-0.2807</v>
+      </c>
+      <c r="V23" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.6642</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484243_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SA TINTINA CB ES CASTELL MENORCA</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
         <v>15.0795</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E24" t="n">
         <v>26.5967</v>
       </c>
-      <c r="F22" t="n">
+      <c r="F24" t="n">
         <v>-11.5173</v>
       </c>
-      <c r="G22" t="n">
-        <v>13.1609</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-2.3472</v>
-      </c>
-      <c r="I22" t="n">
+      <c r="G24" t="n">
+        <v>13.161</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-2.3471</v>
+      </c>
+      <c r="I24" t="n">
         <v>15.5084</v>
       </c>
-      <c r="J22" t="n">
+      <c r="J24" t="n">
         <v>30.5911</v>
       </c>
-      <c r="K22" t="n">
+      <c r="K24" t="n">
         <v>8.331900000000001</v>
       </c>
-      <c r="L22" t="n">
+      <c r="L24" t="n">
         <v>22.259</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M24" t="n">
         <v>-17.43</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N24" t="n">
         <v>-10.6792</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O24" t="n">
         <v>-6.750999999999999</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P24" t="n">
         <v>4.8837</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q24" t="n">
         <v>-11.7205</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R24" t="n">
         <v>16.6041</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S24" t="n">
         <v>-1.582</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T24" t="n">
         <v>0.6886000000000001</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U24" t="n">
         <v>-2.2706</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V24" t="n">
         <v>-1.3831</v>
       </c>
-      <c r="W22" t="n">
-        <v>7.0373</v>
-      </c>
-      <c r="X22" t="n">
+      <c r="W24" t="n">
+        <v>7.037299999999999</v>
+      </c>
+      <c r="X24" t="n">
         <v>-8.4206</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
